--- a/understat_epl_advanced.xlsx
+++ b/understat_epl_advanced.xlsx
@@ -478,621 +478,621 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>81.84</v>
+        <v>11.99</v>
       </c>
       <c r="E2" t="n">
-        <v>93.23999999999999</v>
+        <v>11.73</v>
       </c>
       <c r="F2" t="n">
-        <v>2.45</v>
+        <v>1.96</v>
       </c>
       <c r="G2" t="n">
-        <v>42.32</v>
+        <v>6.65</v>
       </c>
       <c r="H2" t="n">
         <v>1.11</v>
       </c>
       <c r="I2" t="n">
-        <v>50.92</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>72.95999999999999</v>
+        <v>11.72</v>
       </c>
       <c r="E3" t="n">
-        <v>73.56999999999999</v>
+        <v>12.63</v>
       </c>
       <c r="F3" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
-        <v>39.98</v>
+        <v>7.94</v>
       </c>
       <c r="H3" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="I3" t="n">
-        <v>33.59</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>65.03</v>
+        <v>11.42</v>
       </c>
       <c r="E4" t="n">
-        <v>72.62</v>
+        <v>12.24</v>
       </c>
       <c r="F4" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>53.99</v>
+        <v>7.26</v>
       </c>
       <c r="H4" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="I4" t="n">
-        <v>18.63</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>64.66</v>
+        <v>11.19</v>
       </c>
       <c r="E5" t="n">
-        <v>73.15000000000001</v>
+        <v>14.53</v>
       </c>
       <c r="F5" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="G5" t="n">
-        <v>52.9</v>
+        <v>9.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="I5" t="n">
-        <v>20.25</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>62.61</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>71.48</v>
+        <v>11.15</v>
       </c>
       <c r="F6" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G6" t="n">
-        <v>53.98</v>
+        <v>8.73</v>
       </c>
       <c r="H6" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="I6" t="n">
-        <v>17.5</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>62.56</v>
+        <v>9.4</v>
       </c>
       <c r="E7" t="n">
-        <v>73.12</v>
+        <v>11.8</v>
       </c>
       <c r="F7" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="G7" t="n">
-        <v>54.26</v>
+        <v>9.33</v>
       </c>
       <c r="H7" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="I7" t="n">
-        <v>18.86</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>61.53</v>
+        <v>9.35</v>
       </c>
       <c r="E8" t="n">
-        <v>66.39</v>
+        <v>9.77</v>
       </c>
       <c r="F8" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="I8" t="n">
-        <v>11.39</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>58.16</v>
+        <v>8.9</v>
       </c>
       <c r="E9" t="n">
-        <v>67.78</v>
+        <v>11.45</v>
       </c>
       <c r="F9" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="G9" t="n">
-        <v>58.88</v>
+        <v>9.25</v>
       </c>
       <c r="H9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I9" t="n">
-        <v>8.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>57.6</v>
+        <v>8.56</v>
       </c>
       <c r="E10" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>49.23</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="I10" t="n">
-        <v>8.77</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>57.26</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>65.28</v>
+        <v>10.94</v>
       </c>
       <c r="F11" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="G11" t="n">
-        <v>59.12</v>
+        <v>10.49</v>
       </c>
       <c r="H11" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="I11" t="n">
-        <v>6.16</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>54.94</v>
+        <v>7.86</v>
       </c>
       <c r="E12" t="n">
-        <v>67.12</v>
+        <v>8.42</v>
       </c>
       <c r="F12" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>60.86</v>
+        <v>8.73</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="I12" t="n">
-        <v>6.26</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>52.24</v>
+        <v>7.7</v>
       </c>
       <c r="E13" t="n">
-        <v>56.91</v>
+        <v>7.85</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="G13" t="n">
-        <v>60.73</v>
+        <v>10.06</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.82</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>50.07</v>
+        <v>7.21</v>
       </c>
       <c r="E14" t="n">
-        <v>65.36</v>
+        <v>10.32</v>
       </c>
       <c r="F14" t="n">
         <v>1.72</v>
       </c>
       <c r="G14" t="n">
-        <v>68.23</v>
+        <v>11.97</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.87</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>50.01</v>
+        <v>6.82</v>
       </c>
       <c r="E15" t="n">
-        <v>52.75</v>
+        <v>9.74</v>
       </c>
       <c r="F15" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="G15" t="n">
-        <v>55.92</v>
+        <v>11.69</v>
       </c>
       <c r="H15" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.17</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>47.65</v>
+        <v>6.68</v>
       </c>
       <c r="E16" t="n">
-        <v>46.87</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="G16" t="n">
-        <v>53.66</v>
+        <v>12.09</v>
       </c>
       <c r="H16" t="n">
-        <v>1.41</v>
+        <v>2.02</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.79</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>41.76</v>
+        <v>6.08</v>
       </c>
       <c r="E17" t="n">
-        <v>50.59</v>
+        <v>7.76</v>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G17" t="n">
-        <v>68.09</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="I17" t="n">
-        <v>-17.5</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>41.45</v>
+        <v>6.05</v>
       </c>
       <c r="E18" t="n">
-        <v>45.37</v>
+        <v>7.26</v>
       </c>
       <c r="F18" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="G18" t="n">
-        <v>61.57</v>
+        <v>9.98</v>
       </c>
       <c r="H18" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="I18" t="n">
-        <v>-16.2</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>28.45</v>
+        <v>5.99</v>
       </c>
       <c r="E19" t="n">
-        <v>40.42</v>
+        <v>9.83</v>
       </c>
       <c r="F19" t="n">
-        <v>1.06</v>
+        <v>1.64</v>
       </c>
       <c r="G19" t="n">
-        <v>83.73</v>
+        <v>13.78</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="I19" t="n">
-        <v>-43.31</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>26.43</v>
+        <v>5.75</v>
       </c>
       <c r="E20" t="n">
-        <v>38.06</v>
+        <v>6.83</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="G20" t="n">
-        <v>85.89</v>
+        <v>12.14</v>
       </c>
       <c r="H20" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="I20" t="n">
-        <v>-47.83</v>
+        <v>-5.31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>22.69</v>
+        <v>5.5</v>
       </c>
       <c r="E21" t="n">
-        <v>38.63</v>
+        <v>6.64</v>
       </c>
       <c r="F21" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="G21" t="n">
-        <v>98.34999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="H21" t="n">
-        <v>2.59</v>
+        <v>1.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-59.72</v>
+        <v>-4.17</v>
       </c>
     </row>
   </sheetData>
